--- a/output/full_scan/batch_seq6_2026-08-06.xlsx
+++ b/output/full_scan/batch_seq6_2026-08-06.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O116"/>
+  <dimension ref="A1:O118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1110,21 +1110,21 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>6214</v>
+        <v>6217</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>精誠</t>
+          <t>中探針</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>587.4265983633087</v>
+        <v>594.1350241934139</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>145.5</v>
+        <v>161.5</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,16 +1135,16 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>53.41957472922842</v>
+        <v>44.9191898872507</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>15.23280799197842</v>
+        <v>30.63235767535078</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1.829066550261872</v>
+        <v>0.4511750427722641</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>0.5827419034627273</v>
+        <v>2.136223419318952</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>6416</v>
+        <v>6214</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>瑞祺電通</t>
+          <t>精誠</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>584.2857211889036</v>
+        <v>587.4265983633087</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>103</v>
+        <v>145.5</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,13 +1188,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>60.58115073234572</v>
+        <v>53.41957472922842</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>22.88812169408795</v>
+        <v>15.23280799197842</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.9149560287303468</v>
+        <v>1.829066550261872</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>-0.1127120293311123</v>
+        <v>0.5827419034627273</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>6271</v>
+        <v>6416</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>同欣電</t>
+          <t>瑞祺電通</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>583.35581562417</v>
+        <v>584.2857211889036</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>192</v>
+        <v>103</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,13 +1241,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>46.79436255903588</v>
+        <v>60.58115073234572</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>26.17303738129062</v>
+        <v>22.88812169408795</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>1.468210446007736</v>
+        <v>0.9149560287303468</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>1.127787640809032</v>
+        <v>-0.1127120293311123</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>6206</v>
+        <v>6271</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>飛捷</t>
+          <t>同欣電</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>582.8145163990702</v>
+        <v>583.35581562417</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>144.5</v>
+        <v>192</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,13 +1294,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>62.44043616461953</v>
+        <v>46.79436255903588</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>19.41074406813954</v>
+        <v>26.17303738129062</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1.581451639907017</v>
+        <v>1.468210446007736</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>2.604622511965928</v>
+        <v>1.127787640809032</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>6275</v>
+        <v>6206</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>元山</t>
+          <t>飛捷</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>574.0168803954035</v>
+        <v>582.8145163990702</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>45.25</v>
+        <v>144.5</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,16 +1347,16 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>51.62585673894991</v>
+        <v>62.44043616461953</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>31.2180151717694</v>
+        <v>19.41074406813954</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>2.286311942272808</v>
+        <v>1.581451639907017</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>0.2415208521885816</v>
+        <v>2.604622511965928</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, volume_break, market_above_ma60, hist_turn_positive, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>6414</v>
+        <v>6275</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>樺漢</t>
+          <t>元山</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>573.5650192058798</v>
+        <v>574.0168803954035</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>468</v>
+        <v>45.25</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,16 +1400,16 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>61.25046252811811</v>
+        <v>51.62585673894991</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>22.30206455795946</v>
+        <v>31.2180151717694</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>1.031809426261303</v>
+        <v>2.286311942272808</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>-0.1296446280026231</v>
+        <v>0.2415208521885816</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, volume_break, market_above_ma60, hist_turn_positive, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>6227</v>
+        <v>6414</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>茂綸</t>
+          <t>樺漢</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>568.9941374475684</v>
+        <v>573.5650192058798</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>125</v>
+        <v>468</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,16 +1453,16 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>60.43171876952337</v>
+        <v>61.25046252811811</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>14.47979923968437</v>
+        <v>22.30206455795946</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.6573324473185898</v>
+        <v>1.031809426261303</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>1.751101736258842</v>
+        <v>-0.1296446280026231</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>6197</v>
+        <v>6227</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>佳必琪</t>
+          <t>茂綸</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>568.8332291801665</v>
+        <v>568.9941374475684</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>316.5</v>
+        <v>125</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,16 +1506,16 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>51.51230090757198</v>
+        <v>60.43171876952337</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>20.10976634491108</v>
+        <v>14.47979923968437</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.7394337484824244</v>
+        <v>0.6573324473185898</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0.7638865416294909</v>
+        <v>1.751101736258842</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>6243</v>
+        <v>6197</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>迅杰</t>
+          <t>佳必琪</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>554.2074519255932</v>
+        <v>568.8332291801665</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>45.3</v>
+        <v>316.5</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,13 +1559,13 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>49.36303081427613</v>
+        <v>51.51230090757198</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>27.01432665658492</v>
+        <v>20.10976634491108</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.6283625182269688</v>
+        <v>0.7394337484824244</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>-0.5924957257791803</v>
+        <v>0.7638865416294909</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>6284</v>
+        <v>6243</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>佳邦</t>
+          <t>迅杰</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>544.8860267325725</v>
+        <v>554.2074519255932</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>76.2</v>
+        <v>45.3</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,16 +1612,16 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>41.44695076901563</v>
+        <v>49.36303081427613</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>29.09136878739405</v>
+        <v>27.01432665658492</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.5114229508799124</v>
+        <v>0.6283625182269688</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0.3394005803112234</v>
+        <v>-0.5924957257791803</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, dealer_buy_3d, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>6292</v>
+        <v>6284</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>迅德</t>
+          <t>佳邦</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>515.7564011617585</v>
+        <v>544.8860267325725</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>59.7</v>
+        <v>76.2</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,13 +1665,13 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>59.21287029510761</v>
+        <v>41.44695076901563</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>18.47964623733414</v>
+        <v>29.09136878739405</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>1.306178543853235</v>
+        <v>0.5114229508799124</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>3</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>1.276122214993866</v>
+        <v>0.3394005803112234</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>6451</v>
+        <v>6292</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>訊芯-KY</t>
+          <t>迅德</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>507.3919800888114</v>
+        <v>515.7564011617585</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>452</v>
+        <v>59.7</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,16 +1718,16 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>51.31693524457864</v>
+        <v>59.21287029510761</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>23.75607175356772</v>
+        <v>18.47964623733414</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>2.536095849341847</v>
+        <v>1.306178543853235</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>6.985867111888737</v>
+        <v>1.276122214993866</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>6177</v>
+        <v>6451</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>達麗</t>
+          <t>訊芯-KY</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>505.4555353154266</v>
+        <v>507.3919800888114</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>47.8</v>
+        <v>452</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,13 +1771,13 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>56.84481306927285</v>
+        <v>51.31693524457864</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>24.05310293174232</v>
+        <v>23.75607175356772</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.5958865519469657</v>
+        <v>2.536095849341847</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>-0.0516056564062707</v>
+        <v>6.985867111888737</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>6175</v>
+        <v>6177</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>立敦</t>
+          <t>達麗</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>492.6482252341669</v>
+        <v>505.4555353154266</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>76.90000000000001</v>
+        <v>47.8</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>39.41335977653416</v>
+        <v>56.84481306927285</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>26.46483740657128</v>
+        <v>24.05310293174232</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.2633016413762612</v>
+        <v>0.5958865519469657</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>-0.7359872960467646</v>
+        <v>-0.0516056564062707</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6474</v>
+        <v>6175</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>華豫寧</t>
+          <t>立敦</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>479.0830302837214</v>
+        <v>492.6482252341669</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>37.8</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,16 +1877,16 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>53.18348058661765</v>
+        <v>39.41335977653416</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>6.788984760119471</v>
+        <v>26.46483740657128</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.8068462181664275</v>
+        <v>0.2633016413762612</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.0406646417625716</v>
+        <v>-0.7359872960467646</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>6166</v>
+        <v>6474</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>凌華</t>
+          <t>華豫寧</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>476.1006552294109</v>
+        <v>479.0830302837214</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>145</v>
+        <v>37.8</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,16 +1930,16 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>55.20015224427723</v>
+        <v>53.18348058661765</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>19.12727748146898</v>
+        <v>6.788984760119471</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>1.590022015454935</v>
+        <v>0.8068462181664275</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>-0.2693230325009264</v>
+        <v>0.0406646417625716</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>6441</v>
+        <v>6166</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>廣錠</t>
+          <t>凌華</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>475.2463433221909</v>
+        <v>476.1006552294109</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>21.35</v>
+        <v>145</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,16 +1983,16 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>52.87732266065458</v>
+        <v>55.20015224427723</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>14.66149106682874</v>
+        <v>19.12727748146898</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>3.346283924594811</v>
+        <v>1.590022015454935</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.0604111804837219</v>
+        <v>-0.2693230325009264</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, volume_break, market_above_ma60, hist_turn_positive, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>6277</v>
+        <v>6441</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>宏正</t>
+          <t>廣錠</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>472.7858709420618</v>
+        <v>475.2463433221909</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>75.3</v>
+        <v>21.35</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,16 +2036,16 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>48.75978479621719</v>
+        <v>52.87732266065458</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>38.96883875216171</v>
+        <v>14.66149106682874</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.3415997733736227</v>
+        <v>3.346283924594811</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>-0.213565959327926</v>
+        <v>0.0604111804837219</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>macd_golden_cross, volume_break, market_above_ma60, hist_turn_positive, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>6279</v>
+        <v>6277</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>胡連</t>
+          <t>宏正</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>463.5021442439891</v>
+        <v>472.7858709420618</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>120.5</v>
+        <v>75.3</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,16 +2089,16 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>57.44486229625014</v>
+        <v>48.75978479621719</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>14.87711297004902</v>
+        <v>38.96883875216171</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.9491352696628028</v>
+        <v>0.3415997733736227</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.5065901239713771</v>
+        <v>-0.213565959327926</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>6174</v>
+        <v>6279</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>安碁</t>
+          <t>胡連</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>460.4672076974842</v>
+        <v>463.5021442439891</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>41.5</v>
+        <v>120.5</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,16 +2142,16 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>39.89813884578142</v>
+        <v>57.44486229625014</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>27.53024350706242</v>
+        <v>14.87711297004902</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.7796689413404818</v>
+        <v>0.9491352696628028</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>-0.6272824479717913</v>
+        <v>0.5065901239713771</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>6188</v>
+        <v>6174</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>廣明</t>
+          <t>安碁</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>454.2650129894973</v>
+        <v>460.4672076974842</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>71.90000000000001</v>
+        <v>41.5</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,16 +2195,16 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>49.11595510971412</v>
+        <v>39.89813884578142</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>28.47892220720773</v>
+        <v>27.53024350706242</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.5196081989978483</v>
+        <v>0.7796689413404818</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>0.5664308235008102</v>
+        <v>-0.6272824479717913</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, dealer_buy_3d</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>6426</v>
+        <v>6188</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>統新</t>
+          <t>廣明</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>447.2203465165299</v>
+        <v>454.2650129894973</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>187</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,16 +2248,16 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>55.40766187303439</v>
+        <v>49.11595510971412</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>23.02531625816806</v>
+        <v>28.47892220720773</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>1.609762836102356</v>
+        <v>0.5196081989978483</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>4.28339820130337</v>
+        <v>0.5664308235008102</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>6291</v>
+        <v>6426</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>沛亨</t>
+          <t>統新</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>443.0085694603812</v>
+        <v>447.2203465165299</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>383</v>
+        <v>187</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,16 +2301,16 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>45.61294933282893</v>
+        <v>55.40766187303439</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>30.86772625301018</v>
+        <v>23.02531625816806</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.7218255402958771</v>
+        <v>1.609762836102356</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>7.738128602973383</v>
+        <v>4.28339820130337</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, dealer_buy_3d</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>6165</v>
+        <v>6291</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>浪凡</t>
+          <t>沛亨</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>439.8471555595523</v>
+        <v>443.0085694603812</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>49.5</v>
+        <v>383</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,16 +2354,16 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>51.59768097541775</v>
+        <v>45.61294933282893</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>15.73835146040949</v>
+        <v>30.86772625301018</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>1.284715555955226</v>
+        <v>0.7218255402958771</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>-0.009593133827807999</v>
+        <v>7.738128602973383</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>6435</v>
+        <v>6165</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>大中</t>
+          <t>浪凡</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>437.0201207546781</v>
+        <v>439.8471555595523</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>258.5</v>
+        <v>49.5</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>44.29926523445611</v>
+        <v>51.59768097541775</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>31.68225652548715</v>
+        <v>15.73835146040949</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.5387223694753541</v>
+        <v>1.284715555955226</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>-2.139395367262601</v>
+        <v>-0.009593133827807999</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>6417</v>
+        <v>6435</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>韋僑</t>
+          <t>大中</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>429.1117625868786</v>
+        <v>437.0201207546781</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>118.5</v>
+        <v>258.5</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,16 +2460,16 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>48.30524529011452</v>
+        <v>44.29926523445611</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>23.43610469174924</v>
+        <v>31.68225652548715</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.6985791511843511</v>
+        <v>0.5387223694753541</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.3186569572990301</v>
+        <v>-2.139395367262601</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, hist_turn_positive, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>6456</v>
+        <v>6182</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>GIS-KY</t>
+          <t>合晶</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>428.3543580889005</v>
+        <v>430.2225738758928</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>61.4</v>
+        <v>108</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,13 +2513,13 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>47.14970435980077</v>
+        <v>45.62362068823817</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>21.98962237536324</v>
+        <v>26.76587011205104</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.4634486456183349</v>
+        <v>0.0848347858210057</v>
       </c>
       <c r="K39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>0.114374782759036</v>
+        <v>-3.958228625876058</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>6462</v>
+        <v>6417</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>神盾</t>
+          <t>韋僑</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>415.6840745653518</v>
+        <v>429.1117625868786</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>100</v>
+        <v>118.5</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,16 +2566,16 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>46.466679995649</v>
+        <v>48.30524529011452</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>25.29804737378028</v>
+        <v>23.43610469174924</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.5596501084008697</v>
+        <v>0.6985791511843511</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>0.873617269265722</v>
+        <v>0.3186569572990301</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, hist_turn_positive, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>6432</v>
+        <v>6456</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>今展科</t>
+          <t>GIS-KY</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>414.8041871967047</v>
+        <v>428.3543580889005</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>73.5</v>
+        <v>61.4</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,16 +2619,16 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>51.7776332440848</v>
+        <v>47.14970435980077</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>12.85829547435325</v>
+        <v>21.98962237536324</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.7422474220776416</v>
+        <v>0.4634486456183349</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>-0.1513437928714514</v>
+        <v>0.114374782759036</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>6168</v>
+        <v>6462</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>宏齊</t>
+          <t>神盾</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>402.6478176605514</v>
+        <v>415.6840745653518</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>24.7</v>
+        <v>100</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,16 +2672,16 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>48.6357461958058</v>
+        <v>46.466679995649</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>24.6041600480917</v>
+        <v>25.29804737378028</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.6701605364625925</v>
+        <v>0.5596501084008697</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>0.2711765043437624</v>
+        <v>0.873617269265722</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>6282</v>
+        <v>6432</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>康舒</t>
+          <t>今展科</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>377.6659032290979</v>
+        <v>414.8041871967047</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>48.3</v>
+        <v>73.5</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,16 +2725,16 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>47.34818651486702</v>
+        <v>51.7776332440848</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>25.55794730201656</v>
+        <v>12.85829547435325</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.5008863089722483</v>
+        <v>0.7422474220776416</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0.4515189117910347</v>
+        <v>-0.1513437928714514</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>6204</v>
+        <v>6168</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>艾華</t>
+          <t>宏齊</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>375.9414987990692</v>
+        <v>402.6478176605514</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>76.8</v>
+        <v>24.7</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,16 +2778,16 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>44.31450493057626</v>
+        <v>48.6357461958058</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>36.25298637834229</v>
+        <v>24.6041600480917</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.9980558375716452</v>
+        <v>0.6701605364625925</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>1.123911405823106</v>
+        <v>0.2711765043437624</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>6281</v>
+        <v>6282</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>全國電</t>
+          <t>康舒</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>374.7000864434793</v>
+        <v>377.6659032290979</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>51.7</v>
+        <v>48.3</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,13 +2831,13 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>51.23232021467631</v>
+        <v>47.34818651486702</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>19.08637374985983</v>
+        <v>25.55794730201656</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>1.241808220205037</v>
+        <v>0.5008863089722483</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>-0.0315368734592628</v>
+        <v>0.4515189117910347</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6202</v>
+        <v>6204</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>盛群</t>
+          <t>艾華</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>363.6805460086769</v>
+        <v>375.9414987990692</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>59.3</v>
+        <v>76.8</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,16 +2884,16 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>51.00369134197077</v>
+        <v>44.31450493057626</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>23.01101260094308</v>
+        <v>36.25298637834229</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.4334931879828761</v>
+        <v>0.9980558375716452</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>0.5818393051331125</v>
+        <v>1.123911405823106</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>6477</v>
+        <v>6281</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>安集</t>
+          <t>全國電</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>363.1072429211797</v>
+        <v>374.7000864434793</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>35.25</v>
+        <v>51.7</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,13 +2937,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>46.63118160510655</v>
+        <v>51.23232021467631</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>17.66471537246124</v>
+        <v>19.08637374985983</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.1745717233731644</v>
+        <v>1.241808220205037</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>-0.4755979806449582</v>
+        <v>-0.0315368734592628</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>6257</v>
+        <v>6202</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>矽格</t>
+          <t>盛群</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>363.077119476805</v>
+        <v>363.6805460086769</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>207</v>
+        <v>59.3</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,13 +2990,13 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>47.43628766848051</v>
+        <v>51.00369134197077</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>21.47891168643976</v>
+        <v>23.01101260094308</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.608913352026608</v>
+        <v>0.4334931879828761</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-0.771700833378592</v>
+        <v>0.5818393051331125</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>6470</v>
+        <v>6477</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>宇智</t>
+          <t>安集</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>362.6046984575095</v>
+        <v>363.1072429211797</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>43.4</v>
+        <v>35.25</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,16 +3043,16 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>28.97474483733083</v>
+        <v>46.63118160510655</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>39.32573749208665</v>
+        <v>17.66471537246124</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>1.901439245785656</v>
+        <v>0.1745717233731644</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-0.3558216846062909</v>
+        <v>-0.4755979806449582</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>6215</v>
+        <v>6257</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>和椿</t>
+          <t>矽格</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>361.8719655082538</v>
+        <v>363.077119476805</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>97.09999999999999</v>
+        <v>207</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>48.31374065440254</v>
+        <v>47.43628766848051</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>22.23068939534154</v>
+        <v>21.47891168643976</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>1.609614059113614</v>
+        <v>0.608913352026608</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>0.6461644580007375</v>
+        <v>-0.771700833378592</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>6241</v>
+        <v>6470</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>鑫永洋</t>
+          <t>宇智</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>361.4940349524112</v>
+        <v>362.6046984575095</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>15.4</v>
+        <v>43.4</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,16 +3149,16 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>46.95122726937792</v>
+        <v>28.97474483733083</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>25.53947573531062</v>
+        <v>39.32573749208665</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.6582767279225431</v>
+        <v>1.901439245785656</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-0.2111000436396093</v>
+        <v>-0.3558216846062909</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>6472</v>
+        <v>6215</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>保瑞</t>
+          <t>和椿</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>359.3753725195845</v>
+        <v>361.8719655082538</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>418.5</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>55.25533961196705</v>
+        <v>48.31374065440254</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>18.27068026360334</v>
+        <v>22.23068939534154</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.9333414230472716</v>
+        <v>1.609614059113614</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>2.047133779948775</v>
+        <v>0.6461644580007375</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>6411</v>
+        <v>6241</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>晶焱</t>
+          <t>鑫永洋</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>351.2502731970046</v>
+        <v>361.4940349524112</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>78.3</v>
+        <v>15.4</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>41.72316336323521</v>
+        <v>46.95122726937792</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>28.19902321830304</v>
+        <v>25.53947573531062</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.3840732835780278</v>
+        <v>0.6582767279225431</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>0.259693072317436</v>
+        <v>-0.2111000436396093</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, hist_turn_positive, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>6290</v>
+        <v>6472</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>良維</t>
+          <t>保瑞</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>350.4935011136737</v>
+        <v>359.3753725195845</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>214</v>
+        <v>418.5</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,16 +3308,16 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>35.58894776497976</v>
+        <v>55.25533961196705</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>36.31658968855997</v>
+        <v>18.27068026360334</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>1.276342801508462</v>
+        <v>0.9333414230472716</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>-0.2424717709189678</v>
+        <v>2.047133779948775</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>rsi_strong, market_above_ma60, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>6274</v>
+        <v>6411</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>晶焱</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>349.1301359960278</v>
+        <v>351.2502731970046</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>1530</v>
+        <v>78.3</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,49 +3361,49 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>57.96944441469952</v>
+        <v>41.72316336323521</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>19.98324491649675</v>
+        <v>28.19902321830304</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>2.620744028891704</v>
+        <v>0.3840732835780278</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L55" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M55" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>39.49121305970475</v>
+        <v>0.259693072317436</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, mfi_strong</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, hist_turn_positive, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>6278</v>
+        <v>6290</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>台表科</t>
+          <t>良維</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>340.5536667764674</v>
+        <v>350.4935011136737</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>162.5</v>
+        <v>214</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,16 +3414,16 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>47.26584228959192</v>
+        <v>35.58894776497976</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>30.40616720596444</v>
+        <v>36.31658968855997</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>1.875646591654145</v>
+        <v>1.276342801508462</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>1.938328468904009</v>
+        <v>-0.2424717709189678</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>6409</v>
+        <v>6274</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>旭隼</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>329.391396147746</v>
+        <v>349.1301359960278</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>1010</v>
+        <v>1530</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,49 +3467,49 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>53.30436080645772</v>
+        <v>57.96944441469952</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>19.2060754736663</v>
+        <v>19.98324491649675</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.8416889050229952</v>
+        <v>2.620744028891704</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L57" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M57" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>-5.812526332759864</v>
+        <v>39.49121305970475</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>6229</v>
+        <v>6278</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>研通</t>
+          <t>台表科</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>323.4425974684616</v>
+        <v>340.5536667764674</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>23.7</v>
+        <v>162.5</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,16 +3520,16 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>45.10464368779654</v>
+        <v>47.26584228959192</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>24.4310938418739</v>
+        <v>30.40616720596444</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.5083351527541621</v>
+        <v>1.875646591654145</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>0.1073772944078348</v>
+        <v>1.938328468904009</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, foreign_buy_3d, adx_trending</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>6423</v>
+        <v>6409</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>億而得-創</t>
+          <t>旭隼</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>321.6558895807717</v>
+        <v>329.391396147746</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>76.09999999999999</v>
+        <v>1010</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,13 +3573,13 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>52.77336280075148</v>
+        <v>53.30436080645772</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>27.06938359277618</v>
+        <v>19.2060754736663</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>1.154813362539571</v>
+        <v>0.8416889050229952</v>
       </c>
       <c r="K59" s="2" t="n">
         <v>0</v>
@@ -3591,51 +3591,51 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>1.206081786434593</v>
+        <v>-5.812526332759864</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>6288</v>
+        <v>6229</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>聯嘉</t>
+          <t>研通</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>316.7458003679599</v>
+        <v>323.4425974684616</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>20.95</v>
+        <v>23.7</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G60" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>46.89260182677044</v>
+        <v>45.10464368779654</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>30.00690954050626</v>
+        <v>24.4310938418739</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.6831032524092705</v>
+        <v>0.5083351527541621</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>0.0483712616274733</v>
+        <v>0.1073772944078348</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>6191</v>
+        <v>6423</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>精成科</t>
+          <t>億而得-創</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>312.3675865653354</v>
+        <v>321.6558895807717</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>84.90000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>40.4792673486716</v>
+        <v>52.77336280075148</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>33.04729770617336</v>
+        <v>27.06938359277618</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.556197290721209</v>
+        <v>1.154813362539571</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,51 +3697,51 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>-0.1786037693736375</v>
+        <v>1.206081786434593</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>6194</v>
+        <v>6288</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>育富</t>
+          <t>聯嘉</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>310.7183864150256</v>
+        <v>316.7458003679599</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>29.65</v>
+        <v>20.95</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="G62" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>36.65128967793839</v>
+        <v>46.89260182677044</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>29.67331688582057</v>
+        <v>30.00690954050626</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.6221358618103545</v>
+        <v>0.6831032524092705</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>0.0258203133355579</v>
+        <v>0.0483712616274733</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
+          <t>avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>6239</v>
+        <v>6191</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>精成科</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>310.2071455209607</v>
+        <v>312.3675865653354</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>269.5</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>47.03264648199</v>
+        <v>40.4792673486716</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>18.62196291149504</v>
+        <v>33.04729770617336</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.8466581640216754</v>
+        <v>0.556197290721209</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>-0.09612743323133439</v>
+        <v>-0.1786037693736375</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, liquidity_ok, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>6220</v>
+        <v>6194</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>岳豐</t>
+          <t>育富</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>305.9708903778659</v>
+        <v>310.7183864150256</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>26.65</v>
+        <v>29.65</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,16 +3838,16 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>38.62773597132031</v>
+        <v>36.65128967793839</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>31.3165990464518</v>
+        <v>29.67331688582057</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.2364567975655281</v>
+        <v>0.6221358618103545</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-0.0652739496733927</v>
+        <v>0.0258203133355579</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, adx_trending, dealer_buy_3d</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>6266</v>
+        <v>6239</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>泰詠</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>303.8953786787292</v>
+        <v>310.2071455209607</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>24.05</v>
+        <v>269.5</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,16 +3891,16 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>37.16224015898295</v>
+        <v>47.03264648199</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>23.56950587107075</v>
+        <v>18.62196291149504</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>1.070283526851058</v>
+        <v>0.8466581640216754</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>-0.0356977814987744</v>
+        <v>-0.09612743323133439</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>6285</v>
+        <v>6220</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>岳豐</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>293.8066596241056</v>
+        <v>305.9708903778659</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>247</v>
+        <v>26.65</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>50.13797384774892</v>
+        <v>38.62773597132031</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>19.72867292823798</v>
+        <v>31.3165990464518</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>1.352320099453012</v>
+        <v>0.2364567975655281</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>2.272553979856207</v>
+        <v>-0.0652739496733927</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, adx_trending, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>6218</v>
+        <v>6266</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>豪勉</t>
+          <t>泰詠</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>292.6637892306894</v>
+        <v>303.8953786787292</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>34.5</v>
+        <v>24.05</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,16 +3997,16 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>51.45851746320263</v>
+        <v>37.16224015898295</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>12.90921323702955</v>
+        <v>23.56950587107075</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.3701520376687244</v>
+        <v>1.070283526851058</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>0.1534315325032083</v>
+        <v>-0.0356977814987744</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, hist_turn_positive</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>6415</v>
+        <v>6285</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>矽力*-KY</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>291.7649649641265</v>
+        <v>293.8066596241056</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>445</v>
+        <v>247</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>44.96070743066146</v>
+        <v>50.13797384774892</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>22.1429716540617</v>
+        <v>19.72867292823798</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.7131765287890638</v>
+        <v>1.352320099453012</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>2.747862561600769</v>
+        <v>2.272553979856207</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>6183</v>
+        <v>6218</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>關貿</t>
+          <t>豪勉</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>291.0912323050605</v>
+        <v>292.6637892306894</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>91.40000000000001</v>
+        <v>34.5</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,16 +4103,16 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>50.73249247026936</v>
+        <v>51.45851746320263</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>22.20628540266361</v>
+        <v>12.90921323702955</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.5136176753787776</v>
+        <v>0.3701520376687244</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.021233238585004</v>
+        <v>0.1534315325032083</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, hist_turn_positive</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>6449</v>
+        <v>6415</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>鈺邦</t>
+          <t>矽力*-KY</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>290.0329910235355</v>
+        <v>291.7649649641265</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>239</v>
+        <v>445</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>43.08503144991121</v>
+        <v>44.96070743066146</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>32.10464815226521</v>
+        <v>22.1429716540617</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.5877308082641926</v>
+        <v>0.7131765287890638</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,7 +4174,7 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>2.187684181721849</v>
+        <v>2.747862561600769</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
@@ -4184,21 +4184,21 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>6272</v>
+        <v>6183</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>驊陞</t>
+          <t>關貿</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>288.8465575042718</v>
+        <v>291.0912323050605</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>25.15</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,13 +4209,13 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>37.0650889566099</v>
+        <v>50.73249247026936</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>40.93054652153297</v>
+        <v>22.20628540266361</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.5981079908134113</v>
+        <v>0.5136176753787776</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>0.0362239439931066</v>
+        <v>0.021233238585004</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, hist_turn_positive, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>6216</v>
+        <v>6449</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>居易</t>
+          <t>鈺邦</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>288.0647584792839</v>
+        <v>290.0329910235355</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>21.85</v>
+        <v>239</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,13 +4262,13 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>42.21474837122722</v>
+        <v>43.08503144991121</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>15.37075464296761</v>
+        <v>32.10464815226521</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.6179416110744181</v>
+        <v>0.5877308082641926</v>
       </c>
       <c r="K72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>0.009564968741665901</v>
+        <v>2.187684181721849</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>6209</v>
+        <v>6272</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>今國光</t>
+          <t>驊陞</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>287.6779113151444</v>
+        <v>288.8465575042718</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>76.7</v>
+        <v>25.15</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>54.9742415349105</v>
+        <v>37.0650889566099</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>18.65769760952976</v>
+        <v>40.93054652153297</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>1.273320885569662</v>
+        <v>0.5981079908134113</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>1.115659250855829</v>
+        <v>0.0362239439931066</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, hist_turn_positive, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>6442</v>
+        <v>6216</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>居易</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>287.2078293296638</v>
+        <v>288.0647584792839</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>1415</v>
+        <v>21.85</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,13 +4368,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>50.4754745436815</v>
+        <v>42.21474837122722</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>26.3180796417254</v>
+        <v>15.37075464296761</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>1.477260837762707</v>
+        <v>0.6179416110744181</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>35.86326789749688</v>
+        <v>0.009564968741665901</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>6201</v>
+        <v>6209</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>亞弘電</t>
+          <t>今國光</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>286.1625065427722</v>
+        <v>287.6779113151444</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>45.7</v>
+        <v>76.7</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>30.32482738096509</v>
+        <v>54.9742415349105</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>13.83122738965725</v>
+        <v>18.65769760952976</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.283724558736352</v>
+        <v>1.273320885569662</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-0.3526430376670662</v>
+        <v>1.115659250855829</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>6196</v>
+        <v>6442</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>285.8592685255266</v>
+        <v>287.2078293296638</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>508</v>
+        <v>1415</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>48.79706893000861</v>
+        <v>50.4754745436815</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>20.3408938550751</v>
+        <v>26.3180796417254</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.9793445890151274</v>
+        <v>1.477260837762707</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-2.077604632712365</v>
+        <v>35.86326789749688</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>6244</v>
+        <v>6201</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>茂迪</t>
+          <t>亞弘電</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>284.8916456608245</v>
+        <v>286.1625065427722</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>23.75</v>
+        <v>45.7</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>44.86892549186417</v>
+        <v>30.32482738096509</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>21.41241244075613</v>
+        <v>13.83122738965725</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.9939850049263332</v>
+        <v>0.283724558736352</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>0.110361303445676</v>
+        <v>-0.3526430376670662</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>6230</v>
+        <v>6196</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>尼得科超眾</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>283.2958007829382</v>
+        <v>285.8592685255266</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>111</v>
+        <v>508</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,13 +4580,13 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>41.66321054549341</v>
+        <v>48.79706893000861</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>32.95640893533088</v>
+        <v>20.3408938550751</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>1.118103630610761</v>
+        <v>0.9793445890151274</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>0.2133914963786951</v>
+        <v>-2.077604632712365</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, hist_turn_positive, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>6263</v>
+        <v>6244</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>普萊德</t>
+          <t>茂迪</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>280.8700374920911</v>
+        <v>284.8916456608245</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>157</v>
+        <v>23.75</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,16 +4633,16 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>52.33531957632737</v>
+        <v>44.86892549186417</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>13.59229287561781</v>
+        <v>21.41241244075613</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>1.011550241153145</v>
+        <v>0.9939850049263332</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>0.9958086644752696</v>
+        <v>0.110361303445676</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>6208</v>
+        <v>6230</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>日揚</t>
+          <t>尼得科超眾</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>280.1823101882145</v>
+        <v>283.2958007829382</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>81.90000000000001</v>
+        <v>111</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,13 +4686,13 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>44.22794979940873</v>
+        <v>41.66321054549341</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>19.0455383125323</v>
+        <v>32.95640893533088</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.4886826664682964</v>
+        <v>1.118103630610761</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>0.1888532844693058</v>
+        <v>0.2133914963786951</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, dealer_buy_3d</t>
+          <t>macd_golden_cross, market_above_ma60, hist_turn_positive, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>6223</v>
+        <v>6263</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>普萊德</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>276.1307148378074</v>
+        <v>280.8700374920911</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>6300</v>
+        <v>157</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,16 +4739,16 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>54.99093568459385</v>
+        <v>52.33531957632737</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>13.98513819442847</v>
+        <v>13.59229287561781</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.794829972617365</v>
+        <v>1.011550241153145</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>73.34385574705377</v>
+        <v>0.9958086644752696</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>6465</v>
+        <v>6208</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>威潤</t>
+          <t>日揚</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>269.3541198344742</v>
+        <v>280.1823101882145</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>46.9</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,13 +4792,13 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>32.89787182977214</v>
+        <v>44.22794979940873</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>22.37130334238987</v>
+        <v>19.0455383125323</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.5330885368983045</v>
+        <v>0.4886826664682964</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>-0.3951444846389593</v>
+        <v>0.1888532844693058</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>6225</v>
+        <v>6223</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>天瀚</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>267.2702985425417</v>
+        <v>276.1307148378074</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>25.2</v>
+        <v>6300</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,13 +4845,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>55.46545867172693</v>
+        <v>54.99093568459385</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>15.36321513384299</v>
+        <v>13.98513819442847</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>2.604455417489029</v>
+        <v>0.794829972617365</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-0.0693376333025751</v>
+        <v>73.34385574705377</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>6234</v>
+        <v>6465</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>高僑</t>
+          <t>威潤</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>265.2888444615713</v>
+        <v>269.3541198344742</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>34.7</v>
+        <v>46.9</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,16 +4898,16 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>42.63429285033532</v>
+        <v>32.89787182977214</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>33.14199766807923</v>
+        <v>22.37130334238987</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.3607578095988308</v>
+        <v>0.5330885368983045</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>0.2017667382403263</v>
+        <v>-0.3951444846389593</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, foreign_buy_3d, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>6412</v>
+        <v>6225</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>群電</t>
+          <t>天瀚</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>259.6931034341289</v>
+        <v>267.2702985425417</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>78.90000000000001</v>
+        <v>25.2</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,13 +4951,13 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>41.26665283675229</v>
+        <v>55.46545867172693</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>32.84152560038181</v>
+        <v>15.36321513384299</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.9699604405266242</v>
+        <v>2.604455417489029</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>0.2167174333472958</v>
+        <v>-0.0693376333025751</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>6207</v>
+        <v>6234</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>雷科</t>
+          <t>高僑</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>255.3757265569244</v>
+        <v>265.2888444615713</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>104</v>
+        <v>34.7</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,16 +5004,16 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>42.50533572953321</v>
+        <v>42.63429285033532</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>25.63564282345304</v>
+        <v>33.14199766807923</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.3038505613659503</v>
+        <v>0.3607578095988308</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-1.211946632841004</v>
+        <v>0.2017667382403263</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>6464</v>
+        <v>6412</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>台數科</t>
+          <t>群電</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>251.467295085885</v>
+        <v>259.6931034341289</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>77.3</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,13 +5057,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>40.53524018719117</v>
+        <v>41.26665283675229</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>21.12775248742912</v>
+        <v>32.84152560038181</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.2278083724022696</v>
+        <v>0.9699604405266242</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-0.1722505385562898</v>
+        <v>0.2167174333472958</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>6210</v>
+        <v>6207</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>慶生</t>
+          <t>雷科</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>240.6827729783809</v>
+        <v>255.3757265569244</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>17.3</v>
+        <v>104</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,16 +5110,16 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>49.42469747339988</v>
+        <v>42.50533572953321</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>16.94407610121583</v>
+        <v>25.63564282345304</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>3.82527683252602</v>
+        <v>0.3038505613659503</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>0.3890864671935878</v>
+        <v>-1.211946632841004</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>6164</v>
+        <v>6464</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>華興</t>
+          <t>台數科</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>236.7813318508111</v>
+        <v>251.467295085885</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>11.85</v>
+        <v>77.3</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,13 +5163,13 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>43.17801345102657</v>
+        <v>40.53524018719117</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>29.1043880849259</v>
+        <v>21.12775248742912</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.5871337619678257</v>
+        <v>0.2278083724022696</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-0.048967128765225</v>
+        <v>-0.1722505385562898</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>6205</v>
+        <v>6210</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>詮欣</t>
+          <t>慶生</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>231.0707994208222</v>
+        <v>240.6827729783809</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>59.9</v>
+        <v>17.3</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>43.03089683018239</v>
+        <v>49.42469747339988</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>31.26184862969721</v>
+        <v>16.94407610121583</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.7999088112513739</v>
+        <v>3.82527683252602</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>0.6541713094285129</v>
+        <v>0.3890864671935878</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, adx_trending</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>6224</v>
+        <v>6164</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>聚鼎</t>
+          <t>華興</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>229.7440002782521</v>
+        <v>236.7813318508111</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>56.5</v>
+        <v>11.85</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,13 +5269,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>42.25426540639254</v>
+        <v>43.17801345102657</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>33.34897260563335</v>
+        <v>29.1043880849259</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.5710620732309714</v>
+        <v>0.5871337619678257</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
@@ -5287,7 +5287,7 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>0.6381958565821613</v>
+        <v>-0.048967128765225</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
@@ -5297,21 +5297,21 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>6184</v>
+        <v>6205</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>大豐電</t>
+          <t>詮欣</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>229.458084200979</v>
+        <v>231.0707994208222</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>42.3</v>
+        <v>59.9</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>34.33699365836813</v>
+        <v>43.03089683018239</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>20.50187944418031</v>
+        <v>31.26184862969721</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.9058275141535548</v>
+        <v>0.7999088112513739</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>0.08172931818726881</v>
+        <v>0.6541713094285129</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>6192</v>
+        <v>6224</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>巨路</t>
+          <t>聚鼎</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>227.7169677623318</v>
+        <v>229.7440002782521</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>114</v>
+        <v>56.5</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,13 +5375,13 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>45.91770871047376</v>
+        <v>42.25426540639254</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>30.1970105747169</v>
+        <v>33.34897260563335</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.8090735766319738</v>
+        <v>0.5710620732309714</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>0</v>
@@ -5393,7 +5393,7 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>0.2962194962929274</v>
+        <v>0.6381958565821613</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
@@ -5403,21 +5403,21 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>6259</v>
+        <v>6184</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>百徽</t>
+          <t>大豐電</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>212.0663499099419</v>
+        <v>229.458084200979</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>29.9</v>
+        <v>42.3</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,16 +5428,16 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>43.42565258981227</v>
+        <v>34.33699365836813</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>17.01218566442315</v>
+        <v>20.50187944418031</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.2543382757302318</v>
+        <v>0.9058275141535548</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-0.4340037510109575</v>
+        <v>0.08172931818726881</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>6270</v>
+        <v>6192</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>倍微</t>
+          <t>巨路</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>210.7071752706747</v>
+        <v>227.7169677623318</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>29.7</v>
+        <v>114</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>44.6295392723901</v>
+        <v>45.91770871047376</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>20.65429396200584</v>
+        <v>30.1970105747169</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.2642588181655312</v>
+        <v>0.8090735766319738</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,7 +5499,7 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-0.0179955661117976</v>
+        <v>0.2962194962929274</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
@@ -5509,21 +5509,21 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>6237</v>
+        <v>6259</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>驊訊</t>
+          <t>百徽</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>203.5632215459064</v>
+        <v>212.0663499099419</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>33.5</v>
+        <v>29.9</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,16 +5534,16 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>37.4764222930304</v>
+        <v>43.42565258981227</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>36.42829226001657</v>
+        <v>17.01218566442315</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.7121838713671317</v>
+        <v>0.2543382757302318</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>0.2548271255136085</v>
+        <v>-0.4340037510109575</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>6170</v>
+        <v>6270</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>統振</t>
+          <t>倍微</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>202.0875149933932</v>
+        <v>210.7071752706747</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>46.25</v>
+        <v>29.7</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>34.68131922109842</v>
+        <v>44.6295392723901</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>36.6320485532266</v>
+        <v>20.65429396200584</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.2244260532445592</v>
+        <v>0.2642588181655312</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>0.0941355446575515</v>
+        <v>-0.0179955661117976</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>6283</v>
+        <v>6237</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>淳安</t>
+          <t>驊訊</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>201.2344701996744</v>
+        <v>203.5632215459064</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>20</v>
+        <v>33.5</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,16 +5640,16 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>32.03678166804752</v>
+        <v>37.4764222930304</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>35.4855812592705</v>
+        <v>36.42829226001657</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.8749950271914737</v>
+        <v>0.7121838713671317</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>0.0186787337408345</v>
+        <v>0.2548271255136085</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>6438</v>
+        <v>6170</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>迅得</t>
+          <t>統振</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>194.8347763148399</v>
+        <v>202.0875149933932</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>147</v>
+        <v>46.25</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,13 +5693,13 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>50.66546550671829</v>
+        <v>34.68131922109842</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>25.08344556492894</v>
+        <v>36.6320485532266</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.4797655797447234</v>
+        <v>0.2244260532445592</v>
       </c>
       <c r="K99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>0.9265162656349322</v>
+        <v>0.0941355446575515</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>6222</v>
+        <v>6283</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>立軒</t>
+          <t>淳安</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>185.3076208537073</v>
+        <v>201.2344701996744</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>20.3</v>
+        <v>20</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>51.27407822161736</v>
+        <v>32.03678166804752</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>18.25327782070895</v>
+        <v>35.4855812592705</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>1.54009501083649</v>
+        <v>0.8749950271914737</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-0.7528030738248263</v>
+        <v>0.0186787337408345</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, williams_r_recovery</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>6443</v>
+        <v>6438</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>元晶</t>
+          <t>迅得</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>183.5903369070102</v>
+        <v>194.8347763148399</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>26.7</v>
+        <v>147</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>41.62630295777976</v>
+        <v>50.66546550671829</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>30.81095354988338</v>
+        <v>25.08344556492894</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>1.086698061260315</v>
+        <v>0.4797655797447234</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,7 +5817,7 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>0.3225809402788719</v>
+        <v>0.9265162656349322</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
@@ -5827,21 +5827,21 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>6235</v>
+        <v>6222</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>華孚</t>
+          <t>立軒</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>181.9301597531962</v>
+        <v>185.3076208537073</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>39.1</v>
+        <v>20.3</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>48.4808254301724</v>
+        <v>51.27407822161736</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>16.24262263031076</v>
+        <v>18.25327782070895</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.6841548772508139</v>
+        <v>1.54009501083649</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>0.1125254560327804</v>
+        <v>-0.7528030738248263</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, hist_turn_positive</t>
+          <t>volume_break, market_above_ma60, avoid_chase, williams_r_recovery</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>6233</v>
+        <v>6443</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>旺玖</t>
+          <t>元晶</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>175.7336689546706</v>
+        <v>183.5903369070102</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>20.55</v>
+        <v>26.7</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>39.20347289037441</v>
+        <v>41.62630295777976</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>32.74321443536907</v>
+        <v>30.81095354988338</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.2840682613268502</v>
+        <v>1.086698061260315</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-0.0271786389676629</v>
+        <v>0.3225809402788719</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending</t>
+          <t>market_above_ma60, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>6276</v>
+        <v>6235</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>安鈦克</t>
+          <t>華孚</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>173.3014967235609</v>
+        <v>181.9301597531962</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>20.15</v>
+        <v>39.1</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>41.6111885695673</v>
+        <v>48.4808254301724</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>28.80626826467844</v>
+        <v>16.24262263031076</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.2092525013616224</v>
+        <v>0.6841548772508139</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>0.2445884220475827</v>
+        <v>0.1125254560327804</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>macd_golden_cross, market_above_ma60, hist_turn_positive</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>6228</v>
+        <v>6233</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>全譜</t>
+          <t>旺玖</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>161.2148560377275</v>
+        <v>175.7336689546706</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>17.95</v>
+        <v>20.55</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>51.55709575989829</v>
+        <v>39.20347289037441</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>11.48305246026258</v>
+        <v>32.74321443536907</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.7945153624529452</v>
+        <v>0.2840682613268502</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-0.0949543773033403</v>
+        <v>-0.0271786389676629</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, williams_r_recovery</t>
+          <t>market_above_ma60, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>6185</v>
+        <v>6276</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>幃翔</t>
+          <t>安鈦克</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>160.5893371783174</v>
+        <v>173.3014967235609</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>13.7</v>
+        <v>20.15</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,16 +6064,16 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>42.22614200778766</v>
+        <v>41.6111885695673</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>11.73739298649489</v>
+        <v>28.80626826467844</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>1.120779740663299</v>
+        <v>0.2092525013616224</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-0.021239711093677</v>
+        <v>0.2445884220475827</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>6405</v>
+        <v>6228</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>悅城</t>
+          <t>全譜</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>158.476204099818</v>
+        <v>161.2148560377275</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>39</v>
+        <v>17.95</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,13 +6117,13 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>36.9353733766843</v>
+        <v>51.55709575989829</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>32.37753894669128</v>
+        <v>11.48305246026258</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.4965911331659806</v>
+        <v>0.7945153624529452</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>0.6327989676383519</v>
+        <v>-0.0949543773033403</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, williams_r_recovery</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>6418</v>
+        <v>6185</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>詠昇</t>
+          <t>幃翔</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>158.0278239174392</v>
+        <v>160.5893371783174</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>31.85</v>
+        <v>13.7</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,16 +6170,16 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>53.44546269490835</v>
+        <v>42.22614200778766</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>14.10630881988242</v>
+        <v>11.73739298649489</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.6994141850778182</v>
+        <v>1.120779740663299</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>0.1906674269585986</v>
+        <v>-0.021239711093677</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>6485</v>
+        <v>6405</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>點序</t>
+          <t>悅城</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>130.421840556386</v>
+        <v>158.476204099818</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>63.9</v>
+        <v>39</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,16 +6223,16 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>43.48656707174895</v>
+        <v>36.9353733766843</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>34.48876182845854</v>
+        <v>32.37753894669128</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.5447167506125963</v>
+        <v>0.4965911331659806</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>1.067677737158798</v>
+        <v>0.6327989676383519</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>6167</v>
+        <v>6418</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>久正</t>
+          <t>詠昇</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>124.9015010760333</v>
+        <v>158.0278239174392</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>10.4</v>
+        <v>31.85</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>39.78929592508392</v>
+        <v>53.44546269490835</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>23.02701920884984</v>
+        <v>14.10630881988242</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.4017077389753934</v>
+        <v>0.6994141850778182</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>0.0144040490636858</v>
+        <v>0.1906674269585986</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending</t>
+          <t>market_above_ma60, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>6176</v>
+        <v>6485</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>瑞儀</t>
+          <t>點序</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>122.2796870726422</v>
+        <v>130.421840556386</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>84.3</v>
+        <v>63.9</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,16 +6329,16 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>42.57610058739146</v>
+        <v>43.48656707174895</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>19.97942998032501</v>
+        <v>34.48876182845854</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.689768351350532</v>
+        <v>0.5447167506125963</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>0.1502994643955535</v>
+        <v>1.067677737158798</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>6246</v>
+        <v>6167</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>臺龍</t>
+          <t>久正</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>120.481122202595</v>
+        <v>124.9015010760333</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>12.45</v>
+        <v>10.4</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,13 +6382,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>35.53726189826261</v>
+        <v>39.78929592508392</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>28.24934821123401</v>
+        <v>23.02701920884984</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.5751173708920188</v>
+        <v>0.4017077389753934</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
@@ -6400,7 +6400,7 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>-0.0021377416686449</v>
+        <v>0.0144040490636858</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
@@ -6410,21 +6410,21 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>6189</v>
+        <v>6176</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>豐藝</t>
+          <t>瑞儀</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>119.2568526417804</v>
+        <v>122.2796870726422</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>48.95</v>
+        <v>84.3</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,13 +6435,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>50.16644246774319</v>
+        <v>42.57610058739146</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>13.18271068781063</v>
+        <v>19.97942998032501</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.5516254160923548</v>
+        <v>0.689768351350532</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>0.2296658464777352</v>
+        <v>0.1502994643955535</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>6203</v>
+        <v>6246</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>海韻電</t>
+          <t>臺龍</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>96.19702486776588</v>
+        <v>120.481122202595</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>60.6</v>
+        <v>12.45</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,13 +6488,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>29.03271071497961</v>
+        <v>35.53726189826261</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>15.82631657518934</v>
+        <v>28.24934821123401</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.5031482767088155</v>
+        <v>0.5751173708920188</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>-0.4632006337458001</v>
+        <v>-0.0021377416686449</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>6236</v>
+        <v>6189</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>中湛</t>
+          <t>豐藝</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>80</v>
+        <v>119.2568526417804</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>0</v>
+        <v>48.95</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,13 +6541,13 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>48.11588717253862</v>
+        <v>50.16644246774319</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>4.446445132771145</v>
+        <v>13.18271068781063</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>1</v>
+        <v>0.5516254160923548</v>
       </c>
       <c r="K115" s="2" t="n">
         <v>0</v>
@@ -6559,62 +6559,168 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>0.0431847862548719</v>
+        <v>0.2296658464777352</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60</t>
+          <t>ema60_gt_ema120, market_above_ma60</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
+        <v>6203</v>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>海韻電</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D116" s="2" t="n">
+        <v>96.19702486776588</v>
+      </c>
+      <c r="E116" s="2" t="n">
+        <v>60.6</v>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H116" s="2" t="n">
+        <v>29.03271071497961</v>
+      </c>
+      <c r="I116" s="2" t="n">
+        <v>15.82631657518934</v>
+      </c>
+      <c r="J116" s="2" t="n">
+        <v>0.5031482767088155</v>
+      </c>
+      <c r="K116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M116" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N116" s="2" t="n">
+        <v>-0.4632006337458001</v>
+      </c>
+      <c r="O116" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>6236</v>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>中湛</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D117" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="E117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H117" s="2" t="n">
+        <v>48.11588717253862</v>
+      </c>
+      <c r="I117" s="2" t="n">
+        <v>4.446445132771145</v>
+      </c>
+      <c r="J117" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M117" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N117" s="2" t="n">
+        <v>0.0431847862548719</v>
+      </c>
+      <c r="O117" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
         <v>6198</v>
       </c>
-      <c r="B116" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
         <is>
           <t>瑞築</t>
         </is>
       </c>
-      <c r="C116" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D116" s="2" t="n">
+      <c r="C118" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D118" s="2" t="n">
         <v>59.87497241676019</v>
       </c>
-      <c r="E116" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F116" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="G116" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H116" s="2" t="n">
+      <c r="E118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H118" s="2" t="n">
         <v>42.97953614453402</v>
       </c>
-      <c r="I116" s="2" t="n">
+      <c r="I118" s="2" t="n">
         <v>9.473141764259664</v>
       </c>
-      <c r="J116" s="2" t="n">
+      <c r="J118" s="2" t="n">
         <v>0.4180260230426138</v>
       </c>
-      <c r="K116" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L116" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M116" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N116" s="2" t="n">
+      <c r="K118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M118" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N118" s="2" t="n">
         <v>-0.7670310944851337</v>
       </c>
-      <c r="O116" s="2" t="inlineStr">
+      <c r="O118" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60</t>
         </is>
